--- a/AAII_Financials/Quarterly/NGLOY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NGLOY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="92">
   <si>
     <t>NGLOY</t>
   </si>
@@ -656,24 +656,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -684,103 +684,111 @@
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42551</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42369</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42185</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -823,47 +831,53 @@
       <c r="P8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S8" s="3">
         <v>15260000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>10187000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>15098000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>14772000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>13912000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>13698000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>14121000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>12122000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>11442000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>9936000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>8897000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>11558000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>12852000</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -945,8 +959,14 @@
       <c r="AC9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1028,8 +1048,14 @@
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1059,8 +1085,10 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1142,8 +1170,14 @@
       <c r="AC12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1225,8 +1259,14 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1269,47 +1309,53 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
         <v>978000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>133000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>-94000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>231000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>-958000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>323000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>-247000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>88000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>-838000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>1607000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>3527000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>3555000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>4958000</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1352,11 +1398,11 @@
       <c r="P15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1391,8 +1437,14 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1419,8 +1471,10 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1463,47 +1517,53 @@
       <c r="P17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="3">
         <v>10935000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>8453000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>12274000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>11419000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>10346000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>11434000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>11089000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>9753000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>8587000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>10229000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>12104000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>13395000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>16001000</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1546,47 +1606,53 @@
       <c r="P18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="3">
         <v>4325000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>1734000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>2824000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>3353000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>3566000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>2264000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>3032000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>2369000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>2855000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-293000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-3207000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-1837000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-3149000</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1616,8 +1682,10 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1660,47 +1728,53 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="3">
         <v>-234000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>62000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>192000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>306000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>431000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>448000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>331000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>318000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>306000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>91000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-143000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>72000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>116000</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1743,47 +1817,53 @@
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3">
         <v>5505000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>2979000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>4476000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>5011000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>5285000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>4020000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>4656000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>3784000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>4310000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>787000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-2206000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-528000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-1691000</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1826,47 +1906,53 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S22" s="3">
         <v>182000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>241000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>255000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>274000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>249000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>271000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>277000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>268000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>173000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>162000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>184000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>155000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>171000</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1909,47 +1995,53 @@
       <c r="P23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="3">
         <v>3909000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1555000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>2761000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>3385000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>3748000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>2441000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>3086000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>2419000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>2988000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-364000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-3534000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-1920000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-3204000</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1992,47 +2084,53 @@
       <c r="P24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S24" s="3">
         <v>1398000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>738000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>675000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>889000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>1020000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>796000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>801000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>645000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>380000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>318000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-433000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>821000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>435000</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2114,8 +2212,14 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2158,47 +2262,53 @@
       <c r="P26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" s="3">
         <v>2511000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>817000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>2086000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>2496000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>2728000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>1645000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>2285000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>1774000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>2608000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-682000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-3101000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-2741000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-3639000</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2241,47 +2351,53 @@
       <c r="P27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="3">
         <v>1618000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>471000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>1664000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>1883000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>2259000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>1290000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1751000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>1415000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>2407000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-813000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-2609000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-3015000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-3977000</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2363,8 +2479,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2407,11 +2529,11 @@
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2446,8 +2568,14 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2529,8 +2657,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2612,8 +2746,14 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2656,47 +2796,53 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S32" s="3">
         <v>234000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-62000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-192000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-306000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-431000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-448000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-331000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-318000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-306000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-91000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>143000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-72000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-116000</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2739,47 +2885,53 @@
       <c r="P33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S33" s="3">
         <v>1618000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>471000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>1664000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>1883000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>2259000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>1290000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1751000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>1415000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>2407000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-813000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-2609000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-3015000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-3977000</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2861,8 +3013,14 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2905,135 +3063,147 @@
       <c r="P35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="3">
         <v>1618000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>471000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>1664000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>1883000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>2259000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>1290000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1751000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>1415000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>2407000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-813000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-2609000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-3015000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-3977000</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42551</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42369</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42185</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3063,8 +3233,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3094,91 +3266,99 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8863000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>8863000</v>
+      </c>
+      <c r="F41" s="3">
         <v>6436000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>6436000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>5809000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>5809000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>8167000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8167000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>8580000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>8580000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>6088000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>6088000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>7844000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>7844000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>8412000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>7164000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>6321000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>6345000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>7133000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>6567000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>6277000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>7800000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>7408000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>6051000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>5761000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>6895000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>7033000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>6748000</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3189,44 +3369,44 @@
         <v>2000</v>
       </c>
       <c r="F42" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G42" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H42" s="3">
         <v>2330000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>2330000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>36000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>36000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>25000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>25000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>48000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>48000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>62000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>62000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>38000</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>5</v>
       </c>
@@ -3239,11 +3419,11 @@
       <c r="V42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3260,589 +3440,637 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3385000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3385000</v>
+      </c>
+      <c r="F43" s="3">
         <v>3708000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>3708000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>3142000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3142000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>3226000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>3226000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3891000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3891000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4295000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>4295000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>3769000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3769000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>4684000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>3899000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>2619000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>2516000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>2715000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>2147000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>2057000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>2282000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>2175000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>2562000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>2235000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>2135000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>2450000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>2693000</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2979000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2979000</v>
+      </c>
+      <c r="F44" s="3">
         <v>3013000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>3013000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>3152000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>3152000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>5247000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>5247000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>6108000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>6108000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>6387000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>6387000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>6599000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>6599000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>6598000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>5970000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>5600000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>4319000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>4680000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>4466000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>4312000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>4441000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>4124000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>3727000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>3571000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>4051000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>4630000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>4720000</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4014000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4014000</v>
+      </c>
+      <c r="F45" s="3">
         <v>4743000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>4743000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>4190000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>4190000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>2716000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>2716000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>176000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>176000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>118000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>118000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>240000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>240000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>204000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>462000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>147000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>86000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>124000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>132000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>121000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>81000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>85000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>109000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>128000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>689000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>568000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>147000</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19243000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>19243000</v>
+      </c>
+      <c r="F46" s="3">
         <v>18111000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>18111000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>18623000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>18623000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>19660000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>19660000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>18780000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>18780000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>17327000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>17327000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>18514000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>18514000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>19936000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>17495000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>14687000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>13266000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>14652000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>13312000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>12767000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>14604000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>13792000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>12449000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>11695000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>13770000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>14681000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>14308000</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>786000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>786000</v>
+      </c>
+      <c r="F47" s="3">
         <v>1246000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>1246000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>791000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>791000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>987000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>987000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1316000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1316000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1691000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1691000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1658000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1658000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1446000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>2616000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>2120000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>2443000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>2809000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>2819000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>2994000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>3454000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>3533000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>3621000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>3540000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>3202000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>4528000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>6387000</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>34859000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>34859000</v>
+      </c>
+      <c r="F48" s="3">
         <v>34253000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>34253000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>34687000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>34687000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>40844000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>40844000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>44307000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>44307000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>43949000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>43949000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>41585000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>41585000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>41125000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>36419000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>33547000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>34201000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>32080000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>30898000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>29074000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>30643000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>29246000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>28719000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>29327000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>29621000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>35067000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>38475000</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>506000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>506000</v>
+      </c>
+      <c r="F49" s="3">
         <v>504000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>504000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>841000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>841000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>940000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>940000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1449000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1449000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1479000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1479000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2884000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2884000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2828000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>3103000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>2917000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>3086000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>3082000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>3087000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>3200000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>3323000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>3316000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>3217000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>3403000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>3394000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>3802000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>3912000</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3924,8 +4152,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4007,91 +4241,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1641000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1641000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1566000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1566000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1612000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1612000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>2087000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2087000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1738000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1738000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1793000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1793000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1330000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1330000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1434000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2901000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>2557000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>3156000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2175000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2080000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>2489000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>2537000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>2085000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2143000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>2377000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>2026000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>3535000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>2928000</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4173,91 +4419,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>57656000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>57656000</v>
+      </c>
+      <c r="F54" s="3">
         <v>55994000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>55994000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>57272000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>57272000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>64866000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>64866000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>68403000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>68403000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>66544000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>66544000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>66782000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>66782000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>67407000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>62534000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>55828000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>56152000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>54798000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>52196000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>50524000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>54561000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>51972000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>50149000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>50342000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>52013000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>61613000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>66010000</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4287,8 +4545,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4318,506 +4578,544 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4769000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4769000</v>
+      </c>
+      <c r="F57" s="3">
         <v>4879000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>4879000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3901000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3901000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6092000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>6092000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>5900000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>5900000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>6511000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>6511000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>6045000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>6045000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>7380000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>6692000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>4616000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>5373000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>4737000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>4734000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>4313000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>4501000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>3685000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>3384000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>2690000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>2753000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>3268000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>3515000</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1242000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1242000</v>
+      </c>
+      <c r="F58" s="3">
         <v>1075000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1075000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1926000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1926000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2019000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2019000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2176000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2176000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1740000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1740000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>844000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>844000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1420000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1194000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>2345000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>990000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>578000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>600000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1253000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1351000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1879000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>1806000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>1395000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>1649000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>764000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>1618000</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>942000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>942000</v>
+      </c>
+      <c r="F59" s="3">
         <v>860000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>860000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1031000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1031000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1122000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1122000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1424000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1424000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1104000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1104000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1159000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1159000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1694000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1192000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1103000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>865000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1043000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1502000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1303000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1499000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1412000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1335000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1320000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1437000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1037000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1594000</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6953000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6953000</v>
+      </c>
+      <c r="F60" s="3">
         <v>6840000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6840000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6858000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6858000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>9233000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>9233000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>9500000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>9500000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>9355000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>9355000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>8048000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>8048000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>10494000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>9078000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>8064000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>7228000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>6358000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>6836000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>6869000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>7351000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>6976000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>6525000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>5405000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>5839000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>5069000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>6727000</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>16019000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>16019000</v>
+      </c>
+      <c r="F61" s="3">
         <v>14723000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>14723000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>15065000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>15065000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>16953000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>16953000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>17251000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>17251000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>15823000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>15731000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>16219000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>16219000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>12945000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>12317000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>11638000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>9744000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>9780000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>8371000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>8441000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>10620000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>11056000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>11363000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>14546000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>16318000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>18177000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>16917000</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5423000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>5423000</v>
+      </c>
+      <c r="F62" s="3">
         <v>4902000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>4902000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>4584000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>4584000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>3583000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>3583000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>4243000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>4243000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>3638000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>3730000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>3425000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3425000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>4256000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>8373000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>7253000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>7795000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>7410000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>7157000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>7236000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>7708000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>7463000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>7936000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>8963000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>8514000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>10703000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>10189000</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4899,8 +5197,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4982,8 +5286,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5065,91 +5375,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>34254000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>34254000</v>
+      </c>
+      <c r="F66" s="3">
         <v>31877000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>31877000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>31694000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>31694000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>36333000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>36333000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>37539000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>37539000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>34927000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>34927000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>33578000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>33578000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>33454000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>36710000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>32960000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>31357000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>30153000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>28598000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>28131000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>31589000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>30988000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>31133000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>33929000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>35444000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>39713000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>39593000</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5179,8 +5501,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5262,8 +5586,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5345,8 +5675,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5428,8 +5764,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5511,91 +5853,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>27309000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>27309000</v>
+      </c>
+      <c r="F72" s="3">
         <v>28212000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>28212000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>29717000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>29717000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>36744000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>36744000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>39706000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>39706000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>40860000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>40860000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>42555000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>42555000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>42368000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>37192000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>35994000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>36274000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>36164000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>35302000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>33514000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>32735000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>31423000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>29976000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>27577000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>28301000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>32007000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>35989000</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5677,8 +6031,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5760,8 +6120,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5843,91 +6209,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17159000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>17159000</v>
+      </c>
+      <c r="F76" s="3">
         <v>17975000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>17975000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>19338000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>19338000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>20760000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>20760000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>24092000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>24092000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>25057000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>25057000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>26549000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>26549000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>27318000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>25824000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>22868000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>24795000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>24645000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>23598000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>22393000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>22972000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>20984000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>19016000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>16413000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>16569000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>21900000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>26417000</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6009,96 +6387,108 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42551</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42369</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42185</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6141,47 +6531,53 @@
       <c r="P81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S81" s="3">
         <v>1618000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>471000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>1664000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>1883000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>2259000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>1290000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1751000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>1415000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>2407000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-813000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-2609000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-3015000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-3977000</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6211,91 +6607,99 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>508000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>508000</v>
+      </c>
+      <c r="F83" s="3">
         <v>540000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>540000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>497000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>497000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>726000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>726000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>585500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>585500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>630500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>630500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>592500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>592500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>649500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>1414000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1183000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>1460000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>1352000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>1288000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>1308000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>1293000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>1097000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>1149000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>989000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>1144000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>1237000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>1342000</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6377,8 +6781,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6460,8 +6870,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6543,8 +6959,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6626,8 +7048,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6709,91 +7137,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1480500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1480500</v>
+      </c>
+      <c r="F89" s="3">
         <v>1418500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1418500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1337000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1337000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1841500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1841500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>2210000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>2210000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1726500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1726500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1521500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1521500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>2130500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>5413000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1205000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>4259000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>3405000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>3747000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>3380000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>4328000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>3721000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>2838000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>2561000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1262000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>2715000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>2601000</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6823,91 +7263,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-753000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-753000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-872500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-872500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-797500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-797500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-907000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-907000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1565500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1565500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1372500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1372500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1674500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-2622000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-2088000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-2877000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-1867000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-2124000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-1276000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-1478000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-800000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-1318000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-1100000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-2018000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-2035000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-3307000</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6989,8 +7437,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7072,91 +7526,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-713000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-713000</v>
+      </c>
+      <c r="F94" s="3">
         <v>260000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>260000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1214000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1214000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1151500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1151500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1416000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1416000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1515000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1515000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-1265000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1265000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1677000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-2380000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-2360000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-2896000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-1820000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-1994000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-1104000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-1141000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-806000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>532000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-1057000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-271000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-2343000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-3372000</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7186,74 +7652,76 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>85500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>85500</v>
+      </c>
+      <c r="F96" s="3">
         <v>37000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>37000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>135000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>135000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>261500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>261500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>251500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>251500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>329500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>329500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>452500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>452500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>442500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-347000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-557000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-770000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-652000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-610000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-681000</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -7261,16 +7729,22 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-398000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-680000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-403000</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7352,8 +7826,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7435,8 +7915,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7518,253 +8004,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>451500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>451500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1418500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1418500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1327000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1327000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-863000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-863000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>443000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>443000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1111000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1111000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-500500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-500500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-823000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-2027000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>1311000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-2020000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-1096000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-1358000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-3619000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-2898000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-1655000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-3129000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-2651000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-971000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>24000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-788000</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>34500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-39500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-39500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>5500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>5500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>17500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>17500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-37000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-37000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-32000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-32000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-86500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-86500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-152500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>190000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-179000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-72000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>27000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-106000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-190000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>98000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>101000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>42000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>19000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-164000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-110000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-140000</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1211000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1211000</v>
+      </c>
+      <c r="F102" s="3">
         <v>311500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>311500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1169500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1169500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-212500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-212500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1242500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1242500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-882000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-882000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-281000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-281000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-401500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>1196000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-23000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-729000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>516000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>289000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-1533000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>387000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1361000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>283000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-1128000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-144000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>286000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-1699000</v>
       </c>
     </row>
